--- a/resources/reselling/files/reselling-adv-hurdle-card.xlsx
+++ b/resources/reselling/files/reselling-adv-hurdle-card.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,11 +67,6 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -117,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -147,8 +142,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="73" customWidth="1" min="1" max="1"/>
@@ -578,7 +571,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Per-item costs, normal (postage + packing + allowance + per-order)</t>
+          <t>Per-item costs, normal (shipping + packing + allowance + per-order)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -835,10 +828,6 @@
           <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/reselling/files/reselling-adv-hurdle-card.xlsx
+++ b/resources/reselling/files/reselling-adv-hurdle-card.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -137,9 +137,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -510,14 +507,14 @@
   <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="73" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Buy-hurdle card + consignment threshold (Reselling — Advanced, ch3, ch7, ch9)</t>
         </is>
@@ -530,7 +527,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -588,8 +584,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11" ht="33" customHeight="1">
+    <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Minimum net per item (hurdle × minutes ÷ 60)</t>
@@ -600,7 +595,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1">
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>Settings check</t>
@@ -648,8 +643,7 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17" ht="33" customHeight="1">
+    <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Conservative comp (median of recent solds)</t>
@@ -666,7 +660,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="33" customHeight="1">
+    <row r="18">
       <c r="A18" s="5" t="n">
         <v>28</v>
       </c>
@@ -679,7 +673,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="33" customHeight="1">
+    <row r="19">
       <c r="A19" s="5" t="n">
         <v>34</v>
       </c>
@@ -692,7 +686,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="33" customHeight="1">
+    <row r="20">
       <c r="A20" s="5" t="n">
         <v>40</v>
       </c>
@@ -705,7 +699,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="33" customHeight="1">
+    <row r="21">
       <c r="A21" s="5" t="n">
         <v>45</v>
       </c>
@@ -718,7 +712,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="33" customHeight="1">
+    <row r="22">
       <c r="A22" s="5" t="n">
         <v>50</v>
       </c>
@@ -731,7 +725,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="33" customHeight="1">
+    <row r="23">
       <c r="A23" s="5" t="n">
         <v>60</v>
       </c>
@@ -744,7 +738,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
@@ -752,7 +745,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -770,7 +762,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" ht="33" customHeight="1">
+    <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>Item threshold: comp needed</t>
@@ -806,7 +798,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
@@ -821,11 +812,10 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
+          <t>ePORTS — your ecom source (eports.global)  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
     </row>
